--- a/selenium-ecommerce-automation-framework/testdata/UserData.xlsx
+++ b/selenium-ecommerce-automation-framework/testdata/UserData.xlsx
@@ -3,32 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gchai\Desktop\Saleor\selenium-ecommerce-automation-framework\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CABFB80-C355-4E66-88BB-F6072AC9A01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{0DE7C681-24FC-401E-9BE5-A197BDCB33E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
-  <si>
-    <t>TestCaseID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>FirstName</t>
   </si>
@@ -42,12 +38,6 @@
     <t>Password</t>
   </si>
   <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>TC_USER_001</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
@@ -60,12 +50,6 @@
     <t>Welcome@123</t>
   </si>
   <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>TC_USER_002</t>
-  </si>
-  <si>
     <t>Emma</t>
   </si>
   <si>
@@ -75,9 +59,6 @@
     <t>emma.johnson@testmail.com</t>
   </si>
   <si>
-    <t>TC_USER_003</t>
-  </si>
-  <si>
     <t>Michael</t>
   </si>
   <si>
@@ -87,12 +68,6 @@
     <t>michael.brown@testmail.com</t>
   </si>
   <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>TC_USER_004</t>
-  </si>
-  <si>
     <t>Sophia</t>
   </si>
   <si>
@@ -102,7 +77,7 @@
     <t>sophia.wilson@testmail.com</t>
   </si>
   <si>
-    <t>Manager</t>
+    <t>Confirm Password</t>
   </si>
 </sst>
 </file>
@@ -450,12 +425,12 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="4" max="4" width="29.9296875" customWidth="1"/>
-    <col min="5" max="5" width="13.9296875" customWidth="1"/>
+    <col min="3" max="3" width="29.9296875" customWidth="1"/>
+    <col min="4" max="4" width="13.9296875" customWidth="1"/>
+    <col min="5" max="5" width="11.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,98 +444,83 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>24</v>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="mailto:john.smith@testmail.com" xr:uid="{07925615-4541-44CD-9A74-C2C71D41DCCF}"/>
-    <hyperlink ref="D3" r:id="rId2" display="mailto:emma.johnson@testmail.com" xr:uid="{A40D0E5B-5E56-4B8D-B84C-D6EFD5BFC1E6}"/>
-    <hyperlink ref="D4" r:id="rId3" display="mailto:michael.brown@testmail.com" xr:uid="{2982F8BF-1598-4E17-8FC9-B1810F22B5B3}"/>
-    <hyperlink ref="D5" r:id="rId4" display="mailto:sophia.wilson@testmail.com" xr:uid="{EDB208C2-A67A-41AB-BE91-38ECF206E557}"/>
+    <hyperlink ref="C2" r:id="rId1" display="mailto:john.smith@testmail.com" xr:uid="{07925615-4541-44CD-9A74-C2C71D41DCCF}"/>
+    <hyperlink ref="C3" r:id="rId2" display="mailto:emma.johnson@testmail.com" xr:uid="{A40D0E5B-5E56-4B8D-B84C-D6EFD5BFC1E6}"/>
+    <hyperlink ref="C4" r:id="rId3" display="mailto:michael.brown@testmail.com" xr:uid="{2982F8BF-1598-4E17-8FC9-B1810F22B5B3}"/>
+    <hyperlink ref="C5" r:id="rId4" display="mailto:sophia.wilson@testmail.com" xr:uid="{EDB208C2-A67A-41AB-BE91-38ECF206E557}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
